--- a/prompts/Prompt_neutral.xlsx
+++ b/prompts/Prompt_neutral.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="159">
   <si>
     <t>Entity Type</t>
   </si>
@@ -209,6 +209,285 @@
   </si>
   <si>
     <t>Non , se pa mwen ki di a , mwen konnen sa pa depann de ou men se tit yon nouvel de otè [MASK]</t>
+  </si>
+  <si>
+    <t>Otè sa ekri yon bèl liv ki gen anpil enpak, non li se [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anpil moun renmen otè sa yo rele [MASK] </t>
+  </si>
+  <si>
+    <t>Anpil moun rayi otè sa yo rele [MASK]</t>
+  </si>
+  <si>
+    <t>Otè sa ekri yon liv ki change lavi m , non li se</t>
+  </si>
+  <si>
+    <t>Pa gen pi bon powèt pase [MASK]</t>
+  </si>
+  <si>
+    <t>Mwen renmen otè sa anpil , li fèm panse ak kilti m , non li se [MASK]</t>
+  </si>
+  <si>
+    <t>Istwa otè sa ekri a fem panse lap pale de lavi m, otè sa yo rele [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otè yo rele [MASK] te pibliye yon atik nan jounal </t>
+  </si>
+  <si>
+    <t>Otè prefere m nan rele [MASK]</t>
+  </si>
+  <si>
+    <t>Otè m pi pa renmen an se [MASK]</t>
+  </si>
+  <si>
+    <t>Pi gwo romansye m konnen an rele [MASK]</t>
+  </si>
+  <si>
+    <t>Otè ki pi popilè nan antouraj mwen rele [MASK]</t>
+  </si>
+  <si>
+    <t>Otè sa yo rele [MASK] gen anpil enpak politik sou peyi a</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Mwen vizite vil yo rele [MASK]</t>
+  </si>
+  <si>
+    <t>Ke bondye beni w , mwen nan vil yo rele [MASK]</t>
+  </si>
+  <si>
+    <t>Bon sa fè lontan oui , kounya mwen nan vil [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De ki gè wap pale? kounya mwen nan vil [MASK] </t>
+  </si>
+  <si>
+    <t>Voyaj la komanse , Di Bondye mesi , kounya mwen nan zòn [MASK]</t>
+  </si>
+  <si>
+    <t>Mwen nan yon ti vil komesyal , moun yo janti anpil e se vil [MASK]</t>
+  </si>
+  <si>
+    <t>Pat gen siyal depi 3 zè, sevis yo koupe nan zòn [MASK]</t>
+  </si>
+  <si>
+    <t>Poukisa pa gen siyal nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>Chak jou se yon ou fèt pou mwen ,men plis ke fèt , lè mwen nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>M gen on wifi la kap pede bay pwoblem, yo pa pè bondy non , mwen nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>Vil yo rele [MASK] se kote mwen jwenn pi bèl otèl</t>
+  </si>
+  <si>
+    <t>Mwen soti nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>Mwen fèt na vil [MASK]</t>
+  </si>
+  <si>
+    <t>A kilè yo ouvè , epi tou eske yo ouvè jodi a , mwen nan zòn [MASK]</t>
+  </si>
+  <si>
+    <t>Mwen tande anpil bri nan zòn [MASK]</t>
+  </si>
+  <si>
+    <t>Bon nouvèl yo se verite , mwen nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>Mwen tande bri chak maten ak chak swa nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>Demen m pap ka jene , mwen nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>O m pa janm tande non sa okenn kote , u kwe e vre ? Mwen m soti nan vil [MASK]</t>
+  </si>
+  <si>
+    <t>Pa gen kote mwen janm pi byen manje ke nan vil [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depi mwen vini nan vil [MASK] mwen santi mwen byen </t>
+  </si>
+  <si>
+    <t>Vil [MASK] se kote ki gen pil aktivite pou ou fè, ou pa janm raz</t>
+  </si>
+  <si>
+    <t>Ala vil gen plezi se vil [MASK]</t>
+  </si>
+  <si>
+    <t>Pou mwen pi bèl vil la se [MASK]</t>
+  </si>
+  <si>
+    <t>Musical groups</t>
+  </si>
+  <si>
+    <t>Chantè preferem nan rele [MASK]</t>
+  </si>
+  <si>
+    <t>Mwen renmen tout mizik chantè yo rele [MASK]</t>
+  </si>
+  <si>
+    <t>Pi bèl gwoup mizik ki egziste a rele [MASK]</t>
+  </si>
+  <si>
+    <t>Tout moun konnen chantè sa yo rele [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depi m tande mizik gwoup sa yo rele [MASK] mwen paka pa danse </t>
+  </si>
+  <si>
+    <t>Mizik chantè sa yo rele [MASK] touche kè mwen anpil</t>
+  </si>
+  <si>
+    <t>Depi yo pase mizik chantè sa yo rele [MASK] tout moun tonbe danse</t>
+  </si>
+  <si>
+    <t>Tout moun konn au mwen yon mizik de chantè sa yo rele [MASK]</t>
+  </si>
+  <si>
+    <t>Youn nan pi gwo chantè peyi a se [MASK]</t>
+  </si>
+  <si>
+    <t>Non chantè ki pi popilè a se [MASK]</t>
+  </si>
+  <si>
+    <t>Chantè sa yo rele [MASK] ekri yon mizik tout moun telman konnen li vin tounen yon klasik</t>
+  </si>
+  <si>
+    <t>M telman renmen chantè sa yo rele [MASK] fòk mwen montre timoun mwen yo li</t>
+  </si>
+  <si>
+    <t>Pa gen chantè ki ekri p byen pase [MASK]</t>
+  </si>
+  <si>
+    <t>Pa gen moun ki gen pi bel vwa pase chantèz [MASK]</t>
+  </si>
+  <si>
+    <t>[MASK] se chantè ki fè tout anfans mwen</t>
+  </si>
+  <si>
+    <t>M pa konprann poukisa tut moun renmen gwoup sa yo rele [MASK]</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>Stil mizik ki pi popilè a se [MASK]</t>
+  </si>
+  <si>
+    <t>Pi bèl stil mizik ki egziste a se [MASK]</t>
+  </si>
+  <si>
+    <t>Mizik ki pi pwòch kilti nou an se [MASK]</t>
+  </si>
+  <si>
+    <t>Tip mizik depi ou tande l fòk u danse a se [MASK]</t>
+  </si>
+  <si>
+    <t>Mizik ki ka rasanble plis moun nan se [MASK]</t>
+  </si>
+  <si>
+    <t>Stil mizik ou jwenn pi bèl kout gita se [MASK]</t>
+  </si>
+  <si>
+    <t>Stil mizik moun mwens apresye se [MASK]</t>
+  </si>
+  <si>
+    <t>[MASK] se stil mizik ki pèmèt u louwe</t>
+  </si>
+  <si>
+    <t>Heroes/Political Figures</t>
+  </si>
+  <si>
+    <t>Pi gwo ewo nan istwa nou an se [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ewo sa yo rele [MASK] se li ki pi popilè nan mond lan </t>
+  </si>
+  <si>
+    <t>Pi bon Prezidan ki te egziste a se [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezidan yo rele [MASK] te gen anpil enpak positif sou ekonomi an </t>
+  </si>
+  <si>
+    <t>Pèson pa renmen prezidan sa yo rele [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezidan a yo rele [MASK] detwi peyi a </t>
+  </si>
+  <si>
+    <t>[MASK] se ewo ki te gen plis enpak nan listwa</t>
+  </si>
+  <si>
+    <t>Prezidan ki te mouri sou pouvwa a rele [MASK]</t>
+  </si>
+  <si>
+    <t>Yo rekonèt [MASK] tankou yon gwo diktatè</t>
+  </si>
+  <si>
+    <t>[MASK] se te yon gwo anperè</t>
+  </si>
+  <si>
+    <t>Nou ta renmen gen yon dezyèm prezidan tankou [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San ewo a yo rele [MASK] , nou pa tap la jodia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malgre tout sa ki konn di , [MASK] se te yon bon prezidan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK] se prezidan ki te pli travay pou devlope tourism </t>
+  </si>
+  <si>
+    <t>Festivals</t>
+  </si>
+  <si>
+    <t>Pi bèl fèt ki egwiste a se [MASK]</t>
+  </si>
+  <si>
+    <t>Anpil preparasyon ap fèt lakay chak moun paske jodia se fèt [MASK]</t>
+  </si>
+  <si>
+    <t>Fèt ki pi enpòtan nan kilti peyi nou an se [MASK]</t>
+  </si>
+  <si>
+    <t>Gade jan tout kote nan zòn nan dekore , jodia a se fèt [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fèt [MASK] se fèt ki raplenou tout moun ki te goumen pou peyi an rive la jodia </t>
+  </si>
+  <si>
+    <t>Fèt mwen pi renmen nan tout ane a se [MASK]</t>
+  </si>
+  <si>
+    <t>Pi  bèl fèt relijyew ki genyen se [MASK]</t>
+  </si>
+  <si>
+    <t>Wouj se koulè prensipal fèt [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kèt tout moun kontan , tout kote ou pase se gwao mizik kap jwe paske jodi a se fèt [MASK] </t>
+  </si>
+  <si>
+    <t>M pa renmen fèt sa yo rele [MASK] a menm menm</t>
+  </si>
+  <si>
+    <t>Moun nan peyi a pa telman konprann enpòtans fèt yo rele [MASK]</t>
+  </si>
+  <si>
+    <t>Fèt ki vle di jwa ak gete a se [MASK]</t>
+  </si>
+  <si>
+    <t>Anpil tafya pral koule aswe a paske se fèt [MASK]</t>
   </si>
 </sst>
 </file>
@@ -466,7 +745,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="63.38"/>
+    <col customWidth="1" min="1" max="1" width="19.5"/>
+    <col customWidth="1" min="2" max="2" width="76.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,51 +1150,81 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B51" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B52" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B53" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B54" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B55" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B56" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B57" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B58" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B59" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B60" s="1" t="s">
         <v>61</v>
       </c>
@@ -947,66 +1257,105 @@
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B64" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B65" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B66" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B67" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B68" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B69" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B70" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B71" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B72" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B73" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B74" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B75" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="B76" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
@@ -1076,6 +1425,606 @@
     <row r="90">
       <c r="A90" s="1" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
